--- a/tests/js/fixtures/sample.xlsx
+++ b/tests/js/fixtures/sample.xlsx
@@ -29,10 +29,44 @@
 </comments>
 </file>
 
+<file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <connection id="1" name="C" type="1" refreshedVersion="6" odcFile="C:\Users\ZQX7731\Documents\My Data Sources\q.odc">
+    <dbPr connection="Provider=SQLOLEDB;User ID=ZQX7731;Data Source=db" command="SELECT 1"/>
+  </connection>
+</connections>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Openpyxl ZQX7731</author>
+  </authors>
+  <commentList/>
+</comments>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</externalLink>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
   <person displayName="Person ZQX7731" id="{00000000-0000-0000-0000-000000000001}" userId="ZQX7731@example.org" providerId="AD"/>
 </personList>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" refreshedBy="Refresher ZQX7731" refreshedDate="46000.5" recordCount="0">
+  <cacheSource type="worksheet"/>
+  <cacheFields count="0"/>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Q" connectionId="1"/>
 </file>
 
 <file path=xl/revisions/userNames.xml><?xml version="1.0" encoding="utf-8"?>

--- a/tests/js/fixtures/sample.xlsx
+++ b/tests/js/fixtures/sample.xlsx
@@ -104,4 +104,13 @@
     <DisplayName>ZQX7731</DisplayName>
   </Owner>
 </p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ZQX7731-0000-0000-0000-000000000001}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="ZQX7731-6b5d-4628-b7e0-5b86efa98958"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/tests/js/fixtures/sample.xlsx
+++ b/tests/js/fixtures/sample.xlsx
@@ -113,4 +113,21 @@
     <ds:schemaRef ds:uri="ZQX7731-6b5d-4628-b7e0-5b86efa98958"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/spItem.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="urn:x">
+  <Owner>
+    <DisplayName>ZQX7731</DisplayName>
+  </Owner>
+</p:properties>
+</file>
+
+<file path=customXml/spProps.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ZQX7731-0000-0000-0000-000000000001}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="ZQX7731-6b5d-4628-b7e0-5b86efa98958"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/tests/js/fixtures/sample.xlsx
+++ b/tests/js/fixtures/sample.xlsx
@@ -11,6 +11,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <customWorkbookViews>
+    <customWorkbookView name="ZQX7731 - Personal View" guid="{00000000-0000-0000-0000-000000000005}" windowWidth="800" windowHeight="600" activeSheetId="1"/>
+  </customWorkbookViews>
 </workbook>
 </file>
 
@@ -32,7 +35,10 @@
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <connection id="1" name="C" type="1" refreshedVersion="6" odcFile="C:\Users\ZQX7731\Documents\My Data Sources\q.odc">
-    <dbPr connection="Provider=SQLOLEDB;User ID=ZQX7731;Data Source=db" command="SELECT 1"/>
+    <dbPr connection="Provider=SQLOLEDB;User ID=ZQX7731;Data Source=db" command="SELECT * FROM `C:\Users\ZQX7731\Book1.xlsx`.`Sheet1$`"/>
+  </connection>
+  <connection id="2" name="W" type="4" refreshedVersion="6">
+    <webPr url="file:///C:/Users/ZQX7731/page.htm"/>
   </connection>
 </connections>
 </file>
@@ -47,8 +53,10 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls driveId="b!ZQX7731" itemId="01ZQX7731"/>
+  </externalBook>
 </externalLink>
 </file>
 
@@ -73,6 +81,10 @@
 <users xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1">
   <userInfo guid="{00000000-0000-0000-0000-000000000003}" name="Reviser ZQX7731" id="1" dateTime="2031-02-03T04:05:06Z"/>
 </users>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
